--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,766 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8878,0.0010,0.0143,0.0460</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9665,0.0001,0.0004,0.0409</t>
-  </si>
-  <si>
-    <t>0.0026,0.0001,0.0005,0.9989</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9914,0.0051,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.9923,0.0019,0.0016,0.0017</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9929,0.0030,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.3802,0.0010,0.6090,0.0063</t>
-  </si>
-  <si>
-    <t>0.0095,0.0004,0.9918,0.0006</t>
-  </si>
-  <si>
-    <t>0.1692,0.0002,0.8964,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.9984,0.0006</t>
-  </si>
-  <si>
-    <t>0.4321,0.0012,0.5168,0.0174</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0051,0.9905,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.2320,0.7685,0.0069,0.0020</t>
-  </si>
-  <si>
-    <t>0.0007,0.9981,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.3108,0.0001,0.4915,0.0193</t>
-  </si>
-  <si>
-    <t>0.0137,0.0004,0.9782,0.0029</t>
-  </si>
-  <si>
-    <t>0.0013,0.0000,0.9983,0.0004</t>
-  </si>
-  <si>
-    <t>0.0031,0.0001,0.9940,0.0023</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.9987,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9987,0.0012</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9989,0.0008</t>
-  </si>
-  <si>
-    <t>0.5621,0.0833,0.1622,0.0086</t>
-  </si>
-  <si>
-    <t>0.8825,0.0012,0.1343,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0088</t>
-  </si>
-  <si>
-    <t>0.0012,0.1827,0.9906,0.0004</t>
-  </si>
-  <si>
-    <t>0.9460,0.0164,0.0201,0.0025</t>
-  </si>
-  <si>
-    <t>0.9004,0.0073,0.0485,0.0082</t>
-  </si>
-  <si>
-    <t>0.6325,0.3260,0.0267,0.0013</t>
-  </si>
-  <si>
-    <t>0.0216,0.8948,0.1074,0.0058</t>
-  </si>
-  <si>
-    <t>0.0010,0.0605,0.9399,0.0240</t>
-  </si>
-  <si>
-    <t>0.0015,0.0006,0.9758,0.0788</t>
-  </si>
-  <si>
-    <t>0.0009,0.0007,0.9968,0.0034</t>
-  </si>
-  <si>
-    <t>0.0268,0.0000,0.9771,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.0480,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0103,0.6934,0.6320,0.0012</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9993,0.0006</t>
-  </si>
-  <si>
-    <t>0.0171,0.0080,0.0064,0.9869</t>
-  </si>
-  <si>
-    <t>0.0046,0.9728,0.0307,0.0090</t>
-  </si>
-  <si>
-    <t>0.0007,0.9885,0.0258,0.0168</t>
-  </si>
-  <si>
-    <t>0.0012,0.9964,0.0038,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0012,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0514,0.9967,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9992,0.0010</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.9995,0.0000</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.8730,0.0006,0.0123,0.0655</t>
+  </si>
+  <si>
+    <t>0.0017,0.0000,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.8922,0.0001,0.0019,0.1087</t>
+  </si>
+  <si>
+    <t>0.0040,0.0011,0.0003,0.9983</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9919,0.0055,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9923,0.0024,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.9977,0.0009,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0008,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9936,0.0027,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9976,0.0008,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7323,0.0002,0.3414,0.0014</t>
+  </si>
+  <si>
+    <t>0.0145,0.0010,0.9858,0.0010</t>
+  </si>
+  <si>
+    <t>0.1318,0.0003,0.9198,0.0003</t>
+  </si>
+  <si>
+    <t>0.0036,0.0001,0.9931,0.0023</t>
+  </si>
+  <si>
+    <t>0.8489,0.0037,0.1055,0.0123</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0267,0.9528,0.0132,0.0023</t>
+  </si>
+  <si>
+    <t>0.0879,0.9035,0.0035,0.0018</t>
+  </si>
+  <si>
+    <t>0.0003,0.9992,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.6346,0.0006,0.3546,0.0066</t>
+  </si>
+  <si>
+    <t>0.0298,0.0002,0.9619,0.0031</t>
+  </si>
+  <si>
+    <t>0.0012,0.0000,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0046,0.0002,0.9915,0.0023</t>
+  </si>
+  <si>
+    <t>0.0061,0.0001,0.9947,0.0002</t>
+  </si>
+  <si>
+    <t>0.0974,0.0001,0.8935,0.0063</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9995,0.0094</t>
+  </si>
+  <si>
+    <t>0.0674,0.8335,0.0419,0.0104</t>
+  </si>
+  <si>
+    <t>0.3890,0.0093,0.5876,0.0046</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0028</t>
+  </si>
+  <si>
+    <t>0.0059,0.6605,0.8202,0.0010</t>
+  </si>
+  <si>
+    <t>0.9797,0.0094,0.0035,0.0015</t>
+  </si>
+  <si>
+    <t>0.7030,0.0089,0.1866,0.0121</t>
+  </si>
+  <si>
+    <t>0.5289,0.4528,0.0201,0.0012</t>
+  </si>
+  <si>
+    <t>0.0480,0.8682,0.0683,0.0043</t>
+  </si>
+  <si>
+    <t>0.0024,0.0159,0.9874,0.0064</t>
+  </si>
+  <si>
+    <t>0.0072,0.0005,0.9638,0.0346</t>
+  </si>
+  <si>
+    <t>0.0018,0.0010,0.9959,0.0015</t>
+  </si>
+  <si>
+    <t>0.0032,0.0000,0.9959,0.0006</t>
+  </si>
+  <si>
+    <t>0.0020,0.0069,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9491,0.4273,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0003</t>
+  </si>
+  <si>
+    <t>0.0596,0.0052,0.0128,0.9559</t>
+  </si>
+  <si>
+    <t>0.0009,0.9913,0.0106,0.0071</t>
+  </si>
+  <si>
+    <t>0.0003,0.9914,0.3064,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.9933,0.0138,0.0014</t>
+  </si>
+  <si>
+    <t>0.0004,0.0005,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0124,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.9744,0.0148,0.0031,0.0012</t>
+  </si>
+  <si>
+    <t>0.9978,0.0006,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9952,0.0017,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0021,0.9994,0.0065</t>
+  </si>
+  <si>
+    <t>0.9924,0.0040,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9847,0.0116,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9855,0.0117,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9313,0.9933,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9989,0.0266</t>
+  </si>
+  <si>
+    <t>0.0000,0.9515,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0089</t>
+  </si>
+  <si>
+    <t>0.0010,0.9960,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.0027,0.9957,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.5096,0.0003,0.6961,0.0006</t>
+  </si>
+  <si>
+    <t>0.4595,0.0013,0.6546,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.0014,0.9995,0.0022</t>
+  </si>
+  <si>
+    <t>0.0004,0.5960,0.9924,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9277,0.9920,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9860,0.2930,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9536,0.9548,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0027,0.9992</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.0232,0.9954</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0049,0.9989</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0039,0.9996</t>
+  </si>
+  <si>
+    <t>0.0009,0.8916,0.9190,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.7274,0.9831,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.5278,0.9743,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0015,0.9990,0.0021</t>
+  </si>
+  <si>
+    <t>0.0001,0.5424,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9388,0.9727,0.0000</t>
+  </si>
+  <si>
+    <t>0.9969,0.0010,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9579,0.0290,0.0042,0.0016</t>
+  </si>
+  <si>
+    <t>0.9887,0.0081,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9952,0.0010,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9941,0.0033,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9930,0.0029,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9961,0.0021,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0017,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0015,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9953,0.0023,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0010</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.9974,0.0023</t>
+  </si>
+  <si>
+    <t>0.7100,0.0002,0.0890,0.0381</t>
   </si>
   <si>
     <t>0.0002,0.0000,0.9997,0.0002</t>
   </si>
   <si>
-    <t>0.0007,0.0001,0.9990,0.0003</t>
-  </si>
-  <si>
-    <t>0.9840,0.0077,0.0021,0.0013</t>
-  </si>
-  <si>
-    <t>0.9983,0.0005,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9875,0.0059,0.0027,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.0021,0.9995,0.0036</t>
-  </si>
-  <si>
-    <t>0.9949,0.0028,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9862,0.0113,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9894,0.0059,0.0010,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.9523,0.9529,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9995,0.0030</t>
-  </si>
-  <si>
-    <t>0.0000,0.6904,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0024</t>
-  </si>
-  <si>
-    <t>0.0030,0.9935,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.9991,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7838,0.0001,0.3545,0.0005</t>
-  </si>
-  <si>
-    <t>0.9649,0.0007,0.0371,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0018</t>
-  </si>
-  <si>
-    <t>0.0000,0.9478,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.6516,0.9949,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9942,0.5635,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9434,0.9665,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0031,0.9989</t>
+    <t>0.0093,0.9858,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0757,0.8618,0.0590,0.0066</t>
+  </si>
+  <si>
+    <t>0.0060,0.9878,0.0015,0.0018</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9988,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.2717,0.7261,0.0111,0.0028</t>
+  </si>
+  <si>
+    <t>0.4888,0.0058,0.4963,0.0068</t>
+  </si>
+  <si>
+    <t>0.3860,0.0004,0.5750,0.0111</t>
+  </si>
+  <si>
+    <t>0.4641,0.0096,0.4266,0.0178</t>
+  </si>
+  <si>
+    <t>0.1597,0.0070,0.7980,0.0108</t>
+  </si>
+  <si>
+    <t>0.0026,0.0001,0.0257,0.9902</t>
+  </si>
+  <si>
+    <t>0.0008,0.9942,0.0311,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9984,0.0079,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9959,0.0003,0.3524</t>
+  </si>
+  <si>
+    <t>0.0001,0.9798,0.9531,0.0000</t>
+  </si>
+  <si>
+    <t>0.2143,0.7351,0.0262,0.0009</t>
+  </si>
+  <si>
+    <t>0.6872,0.1435,0.0981,0.0015</t>
+  </si>
+  <si>
+    <t>0.7078,0.2086,0.0514,0.0016</t>
+  </si>
+  <si>
+    <t>0.9950,0.0019,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9950,0.0017,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9953,0.0007,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9913,0.0052,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9942,0.0002,0.0006,0.0025</t>
+  </si>
+  <si>
+    <t>0.9932,0.0017,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.0003,0.7403,0.9617,0.0006</t>
+  </si>
+  <si>
+    <t>0.0012,0.1803,0.9935,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.0002,0.9950,0.0002</t>
+  </si>
+  <si>
+    <t>0.8440,0.0006,0.1846,0.0022</t>
+  </si>
+  <si>
+    <t>0.6897,0.0003,0.3202,0.0043</t>
+  </si>
+  <si>
+    <t>0.0414,0.0001,0.9484,0.0052</t>
+  </si>
+  <si>
+    <t>0.6777,0.0009,0.4020,0.0016</t>
+  </si>
+  <si>
+    <t>0.0035,0.0001,0.0009,0.9982</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.0017,0.9992</t>
+  </si>
+  <si>
+    <t>0.0000,0.9865,0.9507,0.0000</t>
+  </si>
+  <si>
+    <t>0.9931,0.0010,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.2422,0.7561,0.0012,0.0049</t>
+  </si>
+  <si>
+    <t>0.9947,0.0005,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.9399,0.0665,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.9949,0.0005,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.6147,0.0004,0.0009,0.5673</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0014,0.9916,0.0101</t>
+  </si>
+  <si>
+    <t>0.9906,0.0004,0.0019,0.0024</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.4572,0.2715,0.0722,0.0090</t>
+  </si>
+  <si>
+    <t>0.9226,0.0025,0.0345,0.0094</t>
+  </si>
+  <si>
+    <t>0.9818,0.0006,0.0112,0.0010</t>
+  </si>
+  <si>
+    <t>0.8461,0.0088,0.0914,0.0052</t>
+  </si>
+  <si>
+    <t>0.7367,0.0036,0.2725,0.0027</t>
+  </si>
+  <si>
+    <t>0.9581,0.0095,0.0138,0.0013</t>
+  </si>
+  <si>
+    <t>0.9921,0.0024,0.0022,0.0007</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9945,0.0011,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9922,0.0016,0.0015,0.0014</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9960,0.0004,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.7964,0.0797,0.0228,0.0221</t>
+  </si>
+  <si>
+    <t>0.8959,0.1069,0.0046,0.0005</t>
+  </si>
+  <si>
+    <t>0.9221,0.0718,0.0056,0.0006</t>
+  </si>
+  <si>
+    <t>0.0116,0.0679,0.9803,0.0008</t>
+  </si>
+  <si>
+    <t>0.8966,0.0993,0.0024,0.0019</t>
+  </si>
+  <si>
+    <t>0.9779,0.0013,0.0024,0.0082</t>
+  </si>
+  <si>
+    <t>0.9960,0.0011,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9744,0.0034,0.0025,0.0072</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9999,0.0004</t>
+  </si>
+  <si>
+    <t>0.9534,0.0144,0.0153,0.0037</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.9992,0.0003</t>
+  </si>
+  <si>
+    <t>0.0037,0.0000,0.9957,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0022,0.9989,0.0026</t>
+  </si>
+  <si>
+    <t>0.0003,0.0018,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9994,0.0007</t>
+  </si>
+  <si>
+    <t>0.0618,0.0010,0.9343,0.0028</t>
+  </si>
+  <si>
+    <t>0.0390,0.0005,0.9534,0.0042</t>
+  </si>
+  <si>
+    <t>0.2277,0.0026,0.7896,0.0037</t>
+  </si>
+  <si>
+    <t>0.1501,0.0009,0.8933,0.0005</t>
+  </si>
+  <si>
+    <t>0.0352,0.0258,0.9326,0.0025</t>
+  </si>
+  <si>
+    <t>0.5082,0.0011,0.6337,0.0002</t>
+  </si>
+  <si>
+    <t>0.2405,0.0008,0.6286,0.0220</t>
+  </si>
+  <si>
+    <t>0.1934,0.0003,0.8537,0.0019</t>
+  </si>
+  <si>
+    <t>0.2530,0.6838,0.0519,0.0065</t>
+  </si>
+  <si>
+    <t>0.0191,0.9737,0.0045,0.0003</t>
+  </si>
+  <si>
+    <t>0.1549,0.8533,0.0061,0.0012</t>
+  </si>
+  <si>
+    <t>0.8376,0.1466,0.0106,0.0024</t>
+  </si>
+  <si>
+    <t>0.4269,0.6080,0.0046,0.0016</t>
+  </si>
+  <si>
+    <t>0.5490,0.0167,0.3681,0.0053</t>
+  </si>
+  <si>
+    <t>0.9208,0.0002,0.0446,0.0066</t>
+  </si>
+  <si>
+    <t>0.4049,0.0003,0.2442,0.1107</t>
+  </si>
+  <si>
+    <t>0.3366,0.0015,0.7091,0.0023</t>
+  </si>
+  <si>
+    <t>0.0821,0.0008,0.7956,0.0886</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0011</t>
+  </si>
+  <si>
+    <t>0.0016,0.0007,0.9932,0.0065</t>
+  </si>
+  <si>
+    <t>0.0008,0.0014,0.9979,0.0013</t>
+  </si>
+  <si>
+    <t>0.0151,0.0001,0.9891,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9996,0.0011</t>
+  </si>
+  <si>
+    <t>0.9960,0.0017,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9949,0.0015,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9701,0.0159,0.0026,0.0046</t>
+  </si>
+  <si>
+    <t>0.9928,0.0029,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9932,0.0022,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9727,0.0229,0.0018,0.0012</t>
+  </si>
+  <si>
+    <t>0.9878,0.0086,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.0008,0.9975,0.0033</t>
+  </si>
+  <si>
+    <t>0.0112,0.0024,0.9832,0.0025</t>
+  </si>
+  <si>
+    <t>0.8372,0.0003,0.1335,0.0071</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0045</t>
+  </si>
+  <si>
+    <t>0.0001,0.0021,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0042,0.0003,0.9944,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9992,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9980,0.0100</t>
+  </si>
+  <si>
+    <t>0.1085,0.0002,0.7195,0.0428</t>
+  </si>
+  <si>
+    <t>0.6633,0.0003,0.3395,0.0055</t>
+  </si>
+  <si>
+    <t>0.8670,0.0007,0.1099,0.0053</t>
+  </si>
+  <si>
+    <t>0.9956,0.0016,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9939,0.0021,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9953,0.0029,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9952,0.0015,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9938,0.0032,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9962,0.0013,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9936,0.0030,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.0005,0.9971,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0010,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.0114,0.0018,0.9853,0.0006</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.9986,0.0004</t>
+  </si>
+  <si>
+    <t>0.0393,0.0003,0.9338,0.0059</t>
+  </si>
+  <si>
+    <t>0.2177,0.0009,0.8262,0.0016</t>
+  </si>
+  <si>
+    <t>0.0025,0.0001,0.9938,0.0058</t>
+  </si>
+  <si>
+    <t>0.9676,0.0001,0.0004,0.0325</t>
+  </si>
+  <si>
+    <t>0.0033,0.0001,0.0001,0.9989</t>
+  </si>
+  <si>
+    <t>0.0025,0.0000,0.0024,0.9979</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0002,1.0000</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.0000,0.9999</t>
   </si>
   <si>
-    <t>0.0014,0.0001,0.0287,0.9939</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0043,0.9990</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0061,0.9990</t>
-  </si>
-  <si>
-    <t>0.0009,0.9429,0.8508,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.7601,0.9834,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.6225,0.9916,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.2055,0.9971,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.6785,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9819,0.7765,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0020,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9933,0.0032,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9899,0.0062,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9935,0.0015,0.0008,0.0011</t>
-  </si>
-  <si>
-    <t>0.9953,0.0006,0.0001,0.0022</t>
-  </si>
-  <si>
-    <t>0.9899,0.0083,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9791,0.0162,0.0012,0.0013</t>
-  </si>
-  <si>
-    <t>0.9932,0.0038,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9970,0.0016,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9842,0.0082,0.0024,0.0016</t>
-  </si>
-  <si>
-    <t>0.9962,0.0028,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9980,0.0033</t>
-  </si>
-  <si>
-    <t>0.6911,0.0002,0.1103,0.0322</t>
-  </si>
-  <si>
-    <t>0.0034,0.0001,0.9948,0.0008</t>
-  </si>
-  <si>
-    <t>0.0054,0.9932,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0019,0.9966,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0403,0.9349,0.0172,0.0033</t>
-  </si>
-  <si>
-    <t>0.0314,0.9547,0.0035,0.0037</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9967,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.1361,0.8477,0.0080,0.0040</t>
-  </si>
-  <si>
-    <t>0.0168,0.0008,0.9767,0.0039</t>
-  </si>
-  <si>
-    <t>0.4351,0.0007,0.6256,0.0022</t>
-  </si>
-  <si>
-    <t>0.3494,0.0047,0.5546,0.0187</t>
-  </si>
-  <si>
-    <t>0.3394,0.0026,0.3122,0.1139</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.1118,0.9853</t>
-  </si>
-  <si>
-    <t>0.0014,0.9935,0.0163,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.9984,0.0028,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.9946,0.0014,0.0351</t>
-  </si>
-  <si>
-    <t>0.0003,0.9768,0.8925,0.0001</t>
-  </si>
-  <si>
-    <t>0.0930,0.8816,0.0147,0.0005</t>
-  </si>
-  <si>
-    <t>0.5790,0.0785,0.2483,0.0011</t>
-  </si>
-  <si>
-    <t>0.6303,0.1733,0.1244,0.0027</t>
-  </si>
-  <si>
-    <t>0.9947,0.0027,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9958,0.0007,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9924,0.0004,0.0022,0.0019</t>
-  </si>
-  <si>
-    <t>0.9961,0.0010,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9957,0.0016,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9949,0.0009,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.9976,0.0004,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.2517,0.9957,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0240,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0007,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.0021,0.0001,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.7984,0.0006,0.1625,0.0087</t>
-  </si>
-  <si>
-    <t>0.8497,0.0006,0.2012,0.0012</t>
-  </si>
-  <si>
-    <t>0.0718,0.0002,0.8565,0.0199</t>
-  </si>
-  <si>
-    <t>0.7289,0.0017,0.2412,0.0095</t>
-  </si>
-  <si>
-    <t>0.0074,0.0000,0.0012,0.9966</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0015,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9942,0.7978,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0005,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.7368,0.2778,0.0020,0.0038</t>
-  </si>
-  <si>
-    <t>0.9963,0.0003,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9217,0.0766,0.0057,0.0010</t>
-  </si>
-  <si>
-    <t>0.9973,0.0003,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.2647,0.0005,0.0004,0.8916</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0011,0.9730,0.1192</t>
-  </si>
-  <si>
-    <t>0.9729,0.0004,0.0038,0.0116</t>
-  </si>
-  <si>
-    <t>0.9966,0.0002,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.2749,0.3698,0.1160,0.0099</t>
-  </si>
-  <si>
-    <t>0.9842,0.0011,0.0034,0.0023</t>
-  </si>
-  <si>
-    <t>0.9801,0.0022,0.0093,0.0007</t>
-  </si>
-  <si>
-    <t>0.2457,0.0146,0.7069,0.0102</t>
-  </si>
-  <si>
-    <t>0.7254,0.0097,0.2675,0.0011</t>
-  </si>
-  <si>
-    <t>0.8590,0.0106,0.0917,0.0033</t>
-  </si>
-  <si>
-    <t>0.9951,0.0012,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9980,0.0003,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9945,0.0014,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.9892,0.0017,0.0013,0.0023</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9928,0.0018,0.0015,0.0011</t>
-  </si>
-  <si>
-    <t>0.8467,0.0887,0.0175,0.0078</t>
-  </si>
-  <si>
-    <t>0.4576,0.5426,0.0120,0.0006</t>
-  </si>
-  <si>
-    <t>0.9553,0.0412,0.0024,0.0007</t>
-  </si>
-  <si>
-    <t>0.1375,0.0077,0.9076,0.0009</t>
-  </si>
-  <si>
-    <t>0.9923,0.0037,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9923,0.0006,0.0006,0.0030</t>
-  </si>
-  <si>
-    <t>0.9947,0.0022,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.8634,0.0845,0.0261,0.0085</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.9756,0.0036,0.0062,0.0040</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0032,0.9980,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.0014,0.1044,0.9901,0.0009</t>
-  </si>
-  <si>
-    <t>0.0050,0.0004,0.9959,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9992,0.0003</t>
-  </si>
-  <si>
-    <t>0.1277,0.0004,0.8913,0.0021</t>
-  </si>
-  <si>
-    <t>0.0695,0.0001,0.9200,0.0032</t>
-  </si>
-  <si>
-    <t>0.4005,0.0022,0.6776,0.0016</t>
-  </si>
-  <si>
-    <t>0.1599,0.0012,0.8885,0.0004</t>
-  </si>
-  <si>
-    <t>0.0350,0.0267,0.9319,0.0010</t>
-  </si>
-  <si>
-    <t>0.3807,0.0004,0.7596,0.0003</t>
-  </si>
-  <si>
-    <t>0.6790,0.0017,0.2371,0.0159</t>
-  </si>
-  <si>
-    <t>0.2407,0.0005,0.8360,0.0006</t>
-  </si>
-  <si>
-    <t>0.1233,0.8321,0.0326,0.0031</t>
-  </si>
-  <si>
-    <t>0.0022,0.9958,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.6386,0.3973,0.0076,0.0013</t>
-  </si>
-  <si>
-    <t>0.8802,0.1422,0.0018,0.0010</t>
-  </si>
-  <si>
-    <t>0.3748,0.6463,0.0054,0.0022</t>
-  </si>
-  <si>
-    <t>0.5667,0.0083,0.3801,0.0087</t>
-  </si>
-  <si>
-    <t>0.9776,0.0004,0.0138,0.0003</t>
-  </si>
-  <si>
-    <t>0.7341,0.0003,0.1513,0.0199</t>
-  </si>
-  <si>
-    <t>0.4500,0.0017,0.5844,0.0047</t>
-  </si>
-  <si>
-    <t>0.2293,0.0006,0.6785,0.0248</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9995,0.0026</t>
-  </si>
-  <si>
-    <t>0.0027,0.0014,0.9952,0.0006</t>
-  </si>
-  <si>
-    <t>0.0007,0.0008,0.9978,0.0015</t>
-  </si>
-  <si>
-    <t>0.0079,0.0002,0.9877,0.0024</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9992,0.0085</t>
-  </si>
-  <si>
-    <t>0.9970,0.0011,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9922,0.0020,0.0020,0.0008</t>
-  </si>
-  <si>
-    <t>0.9744,0.0067,0.0020,0.0070</t>
-  </si>
-  <si>
-    <t>0.9961,0.0011,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9965,0.0013,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9941,0.0023,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.9961,0.0014,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.0008,0.0007,0.9986,0.0009</t>
-  </si>
-  <si>
-    <t>0.2222,0.0112,0.6844,0.0421</t>
-  </si>
-  <si>
-    <t>0.2653,0.0004,0.5802,0.0406</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9998,0.0185</t>
-  </si>
-  <si>
-    <t>0.0000,0.0012,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.9980,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0004,0.9979,0.0008</t>
-  </si>
-  <si>
-    <t>0.0008,0.0005,0.9976,0.0045</t>
-  </si>
-  <si>
-    <t>0.5525,0.0001,0.5520,0.0013</t>
-  </si>
-  <si>
-    <t>0.7253,0.0012,0.2509,0.0127</t>
-  </si>
-  <si>
-    <t>0.9441,0.0007,0.0267,0.0059</t>
-  </si>
-  <si>
-    <t>0.9940,0.0026,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9981,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9780,0.0204,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9924,0.0029,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9972,0.0008,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9976,0.0008,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9949,0.0031,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9914,0.0046,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.0069,0.0004,0.9925,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0030,0.9981,0.0008</t>
-  </si>
-  <si>
-    <t>0.0026,0.0004,0.9961,0.0005</t>
-  </si>
-  <si>
-    <t>0.0019,0.0000,0.9981,0.0002</t>
-  </si>
-  <si>
-    <t>0.0088,0.0001,0.9539,0.0182</t>
-  </si>
-  <si>
-    <t>0.0041,0.0002,0.9944,0.0012</t>
-  </si>
-  <si>
-    <t>0.0165,0.0002,0.9744,0.0074</t>
-  </si>
-  <si>
-    <t>0.9753,0.0001,0.0012,0.0139</t>
-  </si>
-  <si>
-    <t>0.0032,0.0006,0.0001,0.9987</t>
-  </si>
-  <si>
-    <t>0.0039,0.0000,0.0018,0.9977</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0002,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.5400,0.0005,0.0039,0.5354</t>
+    <t>0.4853,0.0012,0.0023,0.6290</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2009,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2037,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2079,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2093,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2118,10 +2130,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2174,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,7 +2287,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2356,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2370,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2398,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2538,10 +2550,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,7 +2581,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2765,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2779,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2863,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2891,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2902,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2916,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2972,10 +2984,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>265</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,7 +3127,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,7 +3141,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3171,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3283,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3297,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3325,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3381,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3546,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D116" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3574,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3588,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3717,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3731,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3759,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3773,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3787,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3801,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3826,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,7 +3855,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4022,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4078,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4148,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D159" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4190,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4277,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4291,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4333,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4358,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,7 +4387,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,7 +4401,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,7 +4625,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,7 +4639,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,7 +4653,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4652,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4666,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,7 +4709,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4722,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,7 +4765,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4792,10 +4804,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D205" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,7 +4835,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4907,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4935,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5044,10 +5056,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,7 +5185,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5257,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5285,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5299,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5313,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,7 +5521,7 @@
         <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
